--- a/loan_application_forms/044_mortgage_loan_risk_assessment_form--loan_application_forms.xlsx
+++ b/loan_application_forms/044_mortgage_loan_risk_assessment_form--loan_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'5_years'}</t>
+          <t>5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': '5 years'}</t>
+          <t>5 years</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'10_years'}</t>
+          <t>10_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': '10 years'}</t>
+          <t>10 years</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'15_years'}</t>
+          <t>15_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '15 years'}</t>
+          <t>15 years</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'self_employed'}</t>
+          <t>self_employed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Self Employed'}</t>
+          <t>Self Employed</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1324,12 +1324,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'conventional'}</t>
+          <t>conventional</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Conventional'}</t>
+          <t>Conventional</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'government-backed'}</t>
+          <t>government-backed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Government-Backed'}</t>
+          <t>Government-Backed</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'non-conforming'}</t>
+          <t>non-conforming</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Conforming'}</t>
+          <t>Non-Conforming</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1392,12 +1392,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
